--- a/forms/trg/Formulir_TRG_seaj.xlsx
+++ b/forms/trg/Formulir_TRG_seaj.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,14 +925,10 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Romi Librayanto, S.H., M.H.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
+          <t>Prof. Dr. Irwansyah, S.H., M.H.</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
@@ -941,7 +937,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57222996669</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Zulkifli Aspan, S.H., M.H</t>
+          <t>Dr. Romi Librayanto, S.H., M.H.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Marius Olivier, LL.M, Ph.D</t>
+          <t>Dr. Zulkifli Aspan, S.H., M.H</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Ariani Arifin, S.H., M.H.</t>
+          <t>Prof. Marius Olivier, LL.M, Ph.D</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1041,19 +1041,15 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Ilham Arisaputra, S.H., M.Kn.</t>
+          <t>Ariani Arifin, S.H., M.H.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Law Faculty, Hasanuddin Universty</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
@@ -1074,17 +1070,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ahsan Yunus, S.H., M.H.</t>
+          <t>Dr. Muhammad Ilham Arisaputra, S.H., M.Kn.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Law Faculty, Hasanuddin University</t>
+          <t>Law Faculty, Hasanuddin Universty</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1107,15 +1103,19 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Bob Wahyudin, S.H., M.H.</t>
+          <t>Ahsan Yunus, S.H., M.H.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Law Faculty, Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>A. Fatiha Herdinan Nanda</t>
+          <t>Bob Wahyudin, S.H., M.H.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1163,10 +1163,22 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>A. Fatiha Herdinan Nanda</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Power system research group utilizes computational intelligence methods for solving wide-area problems including distributed generation planning, real-time simulation, renewable energy especially photovoltaic system includes MPP control, inverter configuration, partially shaded cases and fault-tolerant for household PV application and intelligent control application to power system includes artificial neural network, fuzzy logic control, genetic algorithm, evolutionary algorithm, particle swarm optimization and chaos theory.</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1174,7 +1186,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1363,15 +1379,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_seaj.xlsx
+++ b/forms/trg/Formulir_TRG_seaj.xlsx
@@ -928,7 +928,11 @@
           <t>Prof. Dr. Irwansyah, S.H., M.H.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
